--- a/r4-ELGA-AustrianPatientSummary-tidy-up/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-tidy-up/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:57:09+00:00</t>
+    <t>2026-02-16T06:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
